--- a/Result/profitability/1323.xlsx
+++ b/Result/profitability/1323.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.355</v>
+        <v>0.19</v>
       </c>
       <c r="N2" t="n">
-        <v>14.8125</v>
+        <v>15.92625</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.43</v>
       </c>
       <c r="M3" t="n">
-        <v>0.16125</v>
+        <v>0.23875</v>
       </c>
       <c r="N3" t="n">
-        <v>16.1975</v>
+        <v>17.29875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -801,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1725</v>
+        <v>0.24875</v>
       </c>
       <c r="N4" t="n">
-        <v>17.10875</v>
+        <v>18.33</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>0.17375</v>
+        <v>0.2625</v>
       </c>
       <c r="N5" t="n">
-        <v>18.25875</v>
+        <v>19.01625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2025</v>
+        <v>0.2787500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>19.1775</v>
+        <v>20.325</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2425</v>
+        <v>0.3</v>
       </c>
       <c r="N7" t="n">
-        <v>20.66</v>
+        <v>21.40875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.46</v>
       </c>
       <c r="M8" t="n">
-        <v>0.275</v>
+        <v>0.3125</v>
       </c>
       <c r="N8" t="n">
-        <v>22.03625</v>
+        <v>22.3425</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>548</v>
+      </c>
+      <c r="D75" t="n">
+        <v>432</v>
+      </c>
+      <c r="E75" t="n">
+        <v>115</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="G75" t="n">
+        <v>40</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.23%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>55</v>
+      </c>
+      <c r="K75" t="n">
+        <v>60</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.41125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.68375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8333333333333335</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.449999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1315083199141169</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.7100000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.059999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.403462050599201</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
